--- a/inst/testdata/water_quality_deployment_tracking_filtered.xlsx
+++ b/inst/testdata/water_quality_deployment_tracking_filtered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Woodside\GitHub Repos\cmpdb\inst\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Woodside\GitHub Repos\cmpr\inst\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11100228-438F-4D9C-AC64-F0D67580B280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA2D930-CE47-48EF-8357-74A5AB23C7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24795" yWindow="2505" windowWidth="19335" windowHeight="11250" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tracker" sheetId="7" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">station_waterbody_county!$A$1:$I$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">station_waterbody_county!$A$1:$J$225</definedName>
     <definedName name="STATION_LIST">#REF!</definedName>
     <definedName name="WATERBODY_LIST">#REF!</definedName>
   </definedNames>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2999" uniqueCount="963">
   <si>
     <t>waterbody</t>
   </si>
@@ -2932,6 +2932,9 @@
   </si>
   <si>
     <t>2025-10-16: DD changed deployment date to match data and Gantt chart</t>
+  </si>
+  <si>
+    <t>lease_num</t>
   </si>
 </sst>
 </file>
@@ -3075,21 +3078,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FC084B48-051C-4EEC-B742-6CBE5E54868C}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -5948,14 +5937,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF3CC64-7BCE-472D-A7C8-0B1372DACC96}">
   <dimension ref="A1:AN91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>254</v>
       </c>
@@ -6077,7 +6066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>45946</v>
       </c>
@@ -6189,7 +6178,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="3" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>45946</v>
       </c>
@@ -6301,7 +6290,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="4" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>45946</v>
       </c>
@@ -6413,7 +6402,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>45946</v>
       </c>
@@ -6525,7 +6514,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>45946</v>
       </c>
@@ -6637,7 +6626,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="7" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>45944</v>
       </c>
@@ -6741,7 +6730,7 @@
       </c>
       <c r="AN7" s="6"/>
     </row>
-    <row r="8" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>45944</v>
       </c>
@@ -6845,7 +6834,7 @@
       </c>
       <c r="AN8" s="6"/>
     </row>
-    <row r="9" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>45944</v>
       </c>
@@ -6949,7 +6938,7 @@
       </c>
       <c r="AN9" s="6"/>
     </row>
-    <row r="10" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>45944</v>
       </c>
@@ -7053,7 +7042,7 @@
       </c>
       <c r="AN10" s="6"/>
     </row>
-    <row r="11" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>45944</v>
       </c>
@@ -7157,7 +7146,7 @@
       </c>
       <c r="AN11" s="6"/>
     </row>
-    <row r="12" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>45944</v>
       </c>
@@ -7247,7 +7236,7 @@
       </c>
       <c r="AN12" s="6"/>
     </row>
-    <row r="13" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>45944</v>
       </c>
@@ -7355,7 +7344,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="14" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>45944</v>
       </c>
@@ -7463,7 +7452,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>45944</v>
       </c>
@@ -7571,7 +7560,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>45944</v>
       </c>
@@ -7679,7 +7668,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="17" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>45944</v>
       </c>
@@ -7787,7 +7776,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="18" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>45944</v>
       </c>
@@ -7895,7 +7884,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>45944</v>
       </c>
@@ -8001,7 +7990,7 @@
       </c>
       <c r="AN19" s="6"/>
     </row>
-    <row r="20" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>45944</v>
       </c>
@@ -8107,7 +8096,7 @@
       </c>
       <c r="AN20" s="6"/>
     </row>
-    <row r="21" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>45944</v>
       </c>
@@ -8213,7 +8202,7 @@
       </c>
       <c r="AN21" s="6"/>
     </row>
-    <row r="22" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>45944</v>
       </c>
@@ -8319,7 +8308,7 @@
       </c>
       <c r="AN22" s="6"/>
     </row>
-    <row r="23" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>45944</v>
       </c>
@@ -8425,7 +8414,7 @@
       </c>
       <c r="AN23" s="6"/>
     </row>
-    <row r="24" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>45944</v>
       </c>
@@ -8531,7 +8520,7 @@
       </c>
       <c r="AN24" s="6"/>
     </row>
-    <row r="25" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>45944</v>
       </c>
@@ -8635,7 +8624,7 @@
       </c>
       <c r="AN25" s="6"/>
     </row>
-    <row r="26" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>45944</v>
       </c>
@@ -8739,7 +8728,7 @@
       </c>
       <c r="AN26" s="6"/>
     </row>
-    <row r="27" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>45944</v>
       </c>
@@ -8845,7 +8834,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="28" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>45944</v>
       </c>
@@ -8949,7 +8938,7 @@
       </c>
       <c r="AN28" s="6"/>
     </row>
-    <row r="29" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>45944</v>
       </c>
@@ -9053,7 +9042,7 @@
       </c>
       <c r="AN29" s="6"/>
     </row>
-    <row r="30" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>45944</v>
       </c>
@@ -9157,7 +9146,7 @@
       </c>
       <c r="AN30" s="6"/>
     </row>
-    <row r="31" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>45944</v>
       </c>
@@ -9247,7 +9236,7 @@
       </c>
       <c r="AN31" s="6"/>
     </row>
-    <row r="32" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>45944</v>
       </c>
@@ -9355,7 +9344,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>45944</v>
       </c>
@@ -9463,7 +9452,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>45944</v>
       </c>
@@ -9571,7 +9560,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="35" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>45944</v>
       </c>
@@ -9679,7 +9668,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>45944</v>
       </c>
@@ -9787,7 +9776,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="37" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>45944</v>
       </c>
@@ -9895,7 +9884,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="38" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>45944</v>
       </c>
@@ -9999,7 +9988,7 @@
       </c>
       <c r="AN38" s="6"/>
     </row>
-    <row r="39" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>45944</v>
       </c>
@@ -10103,7 +10092,7 @@
       </c>
       <c r="AN39" s="6"/>
     </row>
-    <row r="40" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>45944</v>
       </c>
@@ -10207,7 +10196,7 @@
       </c>
       <c r="AN40" s="6"/>
     </row>
-    <row r="41" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>45944</v>
       </c>
@@ -10311,7 +10300,7 @@
       </c>
       <c r="AN41" s="6"/>
     </row>
-    <row r="42" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>45944</v>
       </c>
@@ -10415,7 +10404,7 @@
       </c>
       <c r="AN42" s="6"/>
     </row>
-    <row r="43" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>45944</v>
       </c>
@@ -10521,7 +10510,7 @@
       </c>
       <c r="AN43" s="6"/>
     </row>
-    <row r="44" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>45944</v>
       </c>
@@ -10627,7 +10616,7 @@
       </c>
       <c r="AN44" s="6"/>
     </row>
-    <row r="45" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>45944</v>
       </c>
@@ -10733,7 +10722,7 @@
       </c>
       <c r="AN45" s="6"/>
     </row>
-    <row r="46" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45944</v>
       </c>
@@ -10839,7 +10828,7 @@
       </c>
       <c r="AN46" s="6"/>
     </row>
-    <row r="47" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>45944</v>
       </c>
@@ -10945,7 +10934,7 @@
       </c>
       <c r="AN47" s="6"/>
     </row>
-    <row r="48" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>45944</v>
       </c>
@@ -11051,7 +11040,7 @@
       </c>
       <c r="AN48" s="6"/>
     </row>
-    <row r="49" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>45944</v>
       </c>
@@ -11143,7 +11132,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>45944</v>
       </c>
@@ -11225,7 +11214,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="51" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>45944</v>
       </c>
@@ -11307,7 +11296,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="52" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>45944</v>
       </c>
@@ -11389,7 +11378,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="53" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>45944</v>
       </c>
@@ -11485,7 +11474,7 @@
       <c r="AM53" s="6"/>
       <c r="AN53" s="6"/>
     </row>
-    <row r="54" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>45944</v>
       </c>
@@ -11581,7 +11570,7 @@
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
     </row>
-    <row r="55" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>45944</v>
       </c>
@@ -11677,7 +11666,7 @@
       <c r="AM55" s="6"/>
       <c r="AN55" s="6"/>
     </row>
-    <row r="56" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>45944</v>
       </c>
@@ -11773,7 +11762,7 @@
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
     </row>
-    <row r="57" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>45944</v>
       </c>
@@ -11869,7 +11858,7 @@
       <c r="AM57" s="6"/>
       <c r="AN57" s="6"/>
     </row>
-    <row r="58" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>45944</v>
       </c>
@@ -11965,7 +11954,7 @@
       <c r="AM58" s="6"/>
       <c r="AN58" s="6"/>
     </row>
-    <row r="59" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>45944</v>
       </c>
@@ -12061,7 +12050,7 @@
       <c r="AM59" s="6"/>
       <c r="AN59" s="6"/>
     </row>
-    <row r="60" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>45944</v>
       </c>
@@ -12157,7 +12146,7 @@
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
     </row>
-    <row r="61" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>45944</v>
       </c>
@@ -12253,7 +12242,7 @@
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
     </row>
-    <row r="62" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>45944</v>
       </c>
@@ -12349,7 +12338,7 @@
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
     </row>
-    <row r="63" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>45944</v>
       </c>
@@ -12445,7 +12434,7 @@
       <c r="AM63" s="6"/>
       <c r="AN63" s="6"/>
     </row>
-    <row r="64" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>45944</v>
       </c>
@@ -12539,7 +12528,7 @@
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
     </row>
-    <row r="65" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>45944</v>
       </c>
@@ -12633,7 +12622,7 @@
       <c r="AM65" s="6"/>
       <c r="AN65" s="6"/>
     </row>
-    <row r="66" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>45944</v>
       </c>
@@ -12727,7 +12716,7 @@
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
     </row>
-    <row r="67" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>45944</v>
       </c>
@@ -12821,7 +12810,7 @@
       <c r="AM67" s="6"/>
       <c r="AN67" s="6"/>
     </row>
-    <row r="68" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>45944</v>
       </c>
@@ -12915,7 +12904,7 @@
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
     </row>
-    <row r="69" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>45944</v>
       </c>
@@ -13011,7 +13000,7 @@
       <c r="AM69" s="6"/>
       <c r="AN69" s="6"/>
     </row>
-    <row r="70" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>45944</v>
       </c>
@@ -13107,7 +13096,7 @@
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
     </row>
-    <row r="71" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>45944</v>
       </c>
@@ -13203,7 +13192,7 @@
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
     </row>
-    <row r="72" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>45944</v>
       </c>
@@ -13299,7 +13288,7 @@
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
     </row>
-    <row r="73" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>45944</v>
       </c>
@@ -13395,7 +13384,7 @@
       <c r="AM73" s="6"/>
       <c r="AN73" s="6"/>
     </row>
-    <row r="74" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>45944</v>
       </c>
@@ -13491,7 +13480,7 @@
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
     </row>
-    <row r="75" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>45944</v>
       </c>
@@ -13587,7 +13576,7 @@
       <c r="AM75" s="6"/>
       <c r="AN75" s="6"/>
     </row>
-    <row r="76" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>45944</v>
       </c>
@@ -13683,7 +13672,7 @@
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
     </row>
-    <row r="77" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>45944</v>
       </c>
@@ -13779,7 +13768,7 @@
       <c r="AM77" s="6"/>
       <c r="AN77" s="6"/>
     </row>
-    <row r="78" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>45944</v>
       </c>
@@ -13875,7 +13864,7 @@
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
     </row>
-    <row r="79" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>45944</v>
       </c>
@@ -13971,7 +13960,7 @@
       <c r="AM79" s="6"/>
       <c r="AN79" s="6"/>
     </row>
-    <row r="80" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>45944</v>
       </c>
@@ -14067,7 +14056,7 @@
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
     </row>
-    <row r="81" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>45944</v>
       </c>
@@ -14163,7 +14152,7 @@
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
     </row>
-    <row r="82" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>45944</v>
       </c>
@@ -14259,7 +14248,7 @@
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
     </row>
-    <row r="83" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>45944</v>
       </c>
@@ -14355,7 +14344,7 @@
       <c r="AM83" s="6"/>
       <c r="AN83" s="6"/>
     </row>
-    <row r="84" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>45944</v>
       </c>
@@ -14451,7 +14440,7 @@
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
     </row>
-    <row r="85" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>45944</v>
       </c>
@@ -14547,7 +14536,7 @@
       <c r="AM85" s="6"/>
       <c r="AN85" s="6"/>
     </row>
-    <row r="86" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>45944</v>
       </c>
@@ -14643,7 +14632,7 @@
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
     </row>
-    <row r="87" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>45944</v>
       </c>
@@ -14739,7 +14728,7 @@
       <c r="AM87" s="6"/>
       <c r="AN87" s="6"/>
     </row>
-    <row r="88" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>45944</v>
       </c>
@@ -14835,7 +14824,7 @@
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
     </row>
-    <row r="89" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>45944</v>
       </c>
@@ -14931,7 +14920,7 @@
       <c r="AM89" s="6"/>
       <c r="AN89" s="6"/>
     </row>
-    <row r="90" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>45944</v>
       </c>
@@ -15027,7 +15016,7 @@
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
     </row>
-    <row r="91" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>45944</v>
       </c>
@@ -15128,8 +15117,6 @@
     <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B91">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>ISNA(MATCH($B2,STATION_LIST,0))</formula>
     </cfRule>
@@ -15175,20 +15162,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9178D97-480E-4A1C-A868-3FF779D47BC0}">
-  <dimension ref="A1:I231"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J231"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>1</v>
       </c>
@@ -15199,25 +15187,28 @@
         <v>405</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="18">
         <v>1042</v>
       </c>
@@ -15227,23 +15218,23 @@
       <c r="C2" t="s">
         <v>407</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>44.652859999999997</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>-65.674530000000004</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>438</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>439</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="18">
         <v>5004</v>
       </c>
@@ -15253,23 +15244,23 @@
       <c r="C3" t="s">
         <v>407</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>44.676569999999998</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>-65.691180000000003</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>440</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>441</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="18">
         <v>5005</v>
       </c>
@@ -15279,23 +15270,23 @@
       <c r="C4" t="s">
         <v>407</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>44.634169999999997</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>-65.711929999999995</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>442</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>443</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>5006</v>
       </c>
@@ -15305,23 +15296,23 @@
       <c r="C5" t="s">
         <v>407</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>44.669580000000003</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>-65.647729999999996</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>444</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>445</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>131</v>
       </c>
@@ -15331,23 +15322,23 @@
       <c r="C6" t="s">
         <v>407</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>44.669400000000003</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>-65.644779999999997</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>446</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>447</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>162</v>
       </c>
@@ -15357,23 +15348,23 @@
       <c r="C7" t="s">
         <v>407</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>44.67821</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-65.683350000000004</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>448</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>449</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="18">
         <v>1442</v>
       </c>
@@ -15383,23 +15374,23 @@
       <c r="C8" t="s">
         <v>406</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>45.671616999999998</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>-61.892617000000001</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>450</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>451</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>1443</v>
       </c>
@@ -15410,22 +15401,25 @@
         <v>406</v>
       </c>
       <c r="D9">
+        <v>1443</v>
+      </c>
+      <c r="E9">
         <v>45.679016670000003</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>-61.895583330000001</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>452</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>453</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>213</v>
       </c>
@@ -15435,23 +15429,23 @@
       <c r="C10" t="s">
         <v>406</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>45.659770000000002</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-61.904260000000001</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>454</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>455</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>667</v>
       </c>
@@ -15461,23 +15455,23 @@
       <c r="C11" t="s">
         <v>408</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>45.493409999999997</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>-61.019469999999998</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>456</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>457</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>103</v>
       </c>
@@ -15487,23 +15481,23 @@
       <c r="C12" t="s">
         <v>408</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>45.501350000000002</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-61.041969999999999</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>458</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>459</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>122</v>
       </c>
@@ -15513,23 +15507,23 @@
       <c r="C13" t="s">
         <v>408</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>45.498199999999997</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>-61.019170000000003</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>460</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>461</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>123</v>
       </c>
@@ -15539,23 +15533,23 @@
       <c r="C14" t="s">
         <v>408</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>45.500360000000001</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>-61.018700000000003</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>462</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>463</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>138</v>
       </c>
@@ -15565,23 +15559,23 @@
       <c r="C15" t="s">
         <v>408</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>45.490279999999998</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>-61.038310000000003</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>464</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>465</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>152</v>
       </c>
@@ -15591,23 +15585,23 @@
       <c r="C16" t="s">
         <v>408</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>45.498170000000002</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-61.044649999999997</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>466</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>467</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>154</v>
       </c>
@@ -15617,23 +15611,23 @@
       <c r="C17" t="s">
         <v>408</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>45.498240000000003</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-61.019309999999997</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>468</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>469</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>205</v>
       </c>
@@ -15643,23 +15637,23 @@
       <c r="C18" t="s">
         <v>409</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>44.503349999999998</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>-64.049899999999994</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>470</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>471</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>187</v>
       </c>
@@ -15669,23 +15663,23 @@
       <c r="C19" t="s">
         <v>410</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>46.911230000000003</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-60.474780000000003</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>472</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>473</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>474</v>
       </c>
@@ -15695,23 +15689,23 @@
       <c r="C20" t="s">
         <v>410</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>46.926288999999997</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-60.448709000000001</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>475</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>476</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>156</v>
       </c>
@@ -15721,23 +15715,23 @@
       <c r="C21" t="s">
         <v>408</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>45.529040000000002</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>-60.926009999999998</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>477</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>478</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>343</v>
       </c>
@@ -15747,23 +15741,23 @@
       <c r="C22" t="s">
         <v>410</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>47.013967000000001</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-60.488549999999996</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>479</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>480</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>113</v>
       </c>
@@ -15773,23 +15767,23 @@
       <c r="C23" t="s">
         <v>411</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>44.876849999999997</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-62.399850000000001</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>481</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>482</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>318</v>
       </c>
@@ -15799,17 +15793,17 @@
       <c r="C24" t="s">
         <v>412</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>45.903139000000003</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>-60.72325</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>323</v>
       </c>
@@ -15819,17 +15813,17 @@
       <c r="C25" t="s">
         <v>413</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>45.900416999999997</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>-61.081139</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>338</v>
       </c>
@@ -15839,26 +15833,26 @@
       <c r="C26" t="s">
         <v>414</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>45.673656000000001</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>-62.637242000000001</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>484</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>485</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>894</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>487</v>
       </c>
@@ -15868,23 +15862,23 @@
       <c r="C27" t="s">
         <v>410</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>45.965449999999997</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>-60.79936</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>488</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>489</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>490</v>
       </c>
@@ -15894,23 +15888,23 @@
       <c r="C28" t="s">
         <v>410</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>45.946980000000003</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>-60.809190000000001</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>491</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>492</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>898</v>
       </c>
@@ -15920,17 +15914,17 @@
       <c r="C29" t="s">
         <v>413</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>906</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>907</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
         <v>133</v>
       </c>
@@ -15940,23 +15934,23 @@
       <c r="C30" t="s">
         <v>413</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>45.90399</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>-60.994860000000003</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>493</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>494</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>134</v>
       </c>
@@ -15966,23 +15960,23 @@
       <c r="C31" t="s">
         <v>413</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>45.901029999999999</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>-61.028660000000002</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>495</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>496</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>908</v>
       </c>
@@ -15992,23 +15986,23 @@
       <c r="C32" t="s">
         <v>412</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>45.973419999999997</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>-60.470199999999998</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>497</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>498</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>913</v>
       </c>
@@ -16018,17 +16012,17 @@
       <c r="C33" t="s">
         <v>409</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>915</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>916</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>144</v>
       </c>
@@ -16038,23 +16032,23 @@
       <c r="C34" t="s">
         <v>410</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>46.251370000000001</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>-60.46452</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>499</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>500</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>145</v>
       </c>
@@ -16064,23 +16058,23 @@
       <c r="C35" t="s">
         <v>410</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>46.255479999999999</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>-60.47119</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>501</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>502</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>146</v>
       </c>
@@ -16090,23 +16084,23 @@
       <c r="C36" t="s">
         <v>410</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>46.118409999999997</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-60.62659</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>503</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>504</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>147</v>
       </c>
@@ -16116,23 +16110,23 @@
       <c r="C37" t="s">
         <v>410</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>46.12059</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>-60.633960000000002</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>505</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>506</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>158</v>
       </c>
@@ -16142,23 +16136,23 @@
       <c r="C38" t="s">
         <v>412</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>46.296259999999997</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>-60.287689999999998</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>507</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>508</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>159</v>
       </c>
@@ -16168,23 +16162,23 @@
       <c r="C39" t="s">
         <v>410</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>45.998980000000003</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-60.974339999999998</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>509</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>510</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
         <v>160</v>
       </c>
@@ -16194,23 +16188,23 @@
       <c r="C40" t="s">
         <v>410</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>45.986409999999999</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>-60.990279999999998</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>511</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>512</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
         <v>897</v>
       </c>
@@ -16220,17 +16214,17 @@
       <c r="C41" t="s">
         <v>413</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>904</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>905</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
         <v>900</v>
       </c>
@@ -16240,17 +16234,17 @@
       <c r="C42" t="s">
         <v>412</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>909</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>910</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
         <v>190</v>
       </c>
@@ -16260,23 +16254,23 @@
       <c r="C43" t="s">
         <v>410</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>46.065240000000003</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>-60.894829999999999</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>513</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>514</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
         <v>191</v>
       </c>
@@ -16286,23 +16280,23 @@
       <c r="C44" t="s">
         <v>410</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>46.064779999999999</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>-60.902360000000002</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>515</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>516</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
         <v>899</v>
       </c>
@@ -16312,17 +16306,17 @@
       <c r="C45" t="s">
         <v>410</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>901</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>902</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
         <v>215</v>
       </c>
@@ -16332,23 +16326,23 @@
       <c r="C46" t="s">
         <v>412</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>46.243290000000002</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>-60.303109999999997</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>517</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>518</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
         <v>216</v>
       </c>
@@ -16358,23 +16352,23 @@
       <c r="C47" t="s">
         <v>408</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>45.659550000000003</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-60.864510000000003</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>519</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>520</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
         <v>217</v>
       </c>
@@ -16384,23 +16378,23 @@
       <c r="C48" t="s">
         <v>408</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>45.650790000000001</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>-60.874079999999999</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>521</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>522</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
         <v>527</v>
       </c>
@@ -16410,23 +16404,23 @@
       <c r="C49" t="s">
         <v>408</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>45.710729999999998</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>-61.139620000000001</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>528</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>529</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
         <v>329</v>
       </c>
@@ -16436,17 +16430,17 @@
       <c r="C50" t="s">
         <v>410</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>46.025167000000003</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>-60.863</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
         <v>237</v>
       </c>
@@ -16456,23 +16450,23 @@
       <c r="C51" t="s">
         <v>416</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>43.831530000000001</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>-66.173209999999997</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>530</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>531</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
         <v>232</v>
       </c>
@@ -16482,23 +16476,23 @@
       <c r="C52" t="s">
         <v>414</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>45.756250000000001</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>-62.770310000000002</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>532</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>533</v>
       </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
         <v>74</v>
       </c>
@@ -16508,23 +16502,23 @@
       <c r="C53" t="s">
         <v>414</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>45.669069999999998</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>-62.571899999999999</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>534</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>535</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
         <v>151</v>
       </c>
@@ -16534,23 +16528,23 @@
       <c r="C54" t="s">
         <v>414</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>45.669119999999999</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>-62.572499999999998</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>536</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>537</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
         <v>114</v>
       </c>
@@ -16560,23 +16554,23 @@
       <c r="C55" t="s">
         <v>416</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>43.770389999999999</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>-66.135180000000005</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>538</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>539</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
         <v>135</v>
       </c>
@@ -16586,23 +16580,23 @@
       <c r="C56" t="s">
         <v>417</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>45.359050000000003</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>-61.41966</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>540</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>541</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
         <v>136</v>
       </c>
@@ -16612,26 +16606,26 @@
       <c r="C57" t="s">
         <v>417</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>45.360849999999999</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>-61.407029999999999</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>542</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>543</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>895</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="18" t="s">
         <v>183</v>
       </c>
@@ -16641,23 +16635,23 @@
       <c r="C58" t="s">
         <v>417</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>45.399799999999999</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>-61.420720000000003</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>545</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>546</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
         <v>184</v>
       </c>
@@ -16667,26 +16661,26 @@
       <c r="C59" t="s">
         <v>417</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>45.395000000000003</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>-61.409509999999997</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>547</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>548</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>895</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
         <v>200</v>
       </c>
@@ -16696,23 +16690,23 @@
       <c r="C60" t="s">
         <v>417</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>45.350879999999997</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>-61.26811</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>550</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>551</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>201</v>
       </c>
@@ -16722,26 +16716,26 @@
       <c r="C61" t="s">
         <v>417</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>45.352319999999999</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>-61.28687</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>552</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>553</v>
       </c>
-      <c r="H61" t="s">
+      <c r="I61" t="s">
         <v>895</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
         <v>224</v>
       </c>
@@ -16751,23 +16745,23 @@
       <c r="C62" t="s">
         <v>417</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>45.354930000000003</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>-61.037930000000003</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>555</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>556</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
         <v>225</v>
       </c>
@@ -16777,26 +16771,26 @@
       <c r="C63" t="s">
         <v>417</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>45.361800000000002</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>-61.043999999999997</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>557</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>558</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>895</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18">
         <v>1</v>
       </c>
@@ -16806,23 +16800,23 @@
       <c r="C64" t="s">
         <v>417</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>45.185609999999997</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>-61.716760000000001</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>560</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>561</v>
       </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="18">
         <v>622</v>
       </c>
@@ -16832,23 +16826,23 @@
       <c r="C65" t="s">
         <v>417</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>45.231940000000002</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>-61.76</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>562</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>563</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="18">
         <v>1307</v>
       </c>
@@ -16858,23 +16852,23 @@
       <c r="C66" t="s">
         <v>417</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>45.160069999999997</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>-61.680059999999997</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>564</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>565</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
         <v>234</v>
       </c>
@@ -16884,23 +16878,23 @@
       <c r="C67" t="s">
         <v>417</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>45.173900000000003</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>-61.707540000000002</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>566</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>567</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="18">
         <v>193</v>
       </c>
@@ -16910,23 +16904,23 @@
       <c r="C68" t="s">
         <v>413</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>46.007179999999998</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>-60.98854</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>568</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>569</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
         <v>324</v>
       </c>
@@ -16936,17 +16930,17 @@
       <c r="C69" t="s">
         <v>413</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>46.008028000000003</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>-60.989249999999998</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
         <v>171</v>
       </c>
@@ -16956,23 +16950,23 @@
       <c r="C70" t="s">
         <v>417</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>45.267670000000003</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>-60.979390000000002</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>570</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>571</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
         <v>172</v>
       </c>
@@ -16982,26 +16976,26 @@
       <c r="C71" t="s">
         <v>417</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>45.265799999999999</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>-60.960850000000001</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>572</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>573</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>895</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
         <v>207</v>
       </c>
@@ -17011,23 +17005,23 @@
       <c r="C72" t="s">
         <v>417</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>45.258589999999998</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>-60.999470000000002</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>575</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>576</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
         <v>208</v>
       </c>
@@ -17037,26 +17031,26 @@
       <c r="C73" t="s">
         <v>417</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>45.252470000000002</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>-61.017870000000002</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>577</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>578</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>895</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
         <v>317</v>
       </c>
@@ -17066,17 +17060,17 @@
       <c r="C74" t="s">
         <v>412</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>46.015694000000003</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>-60.393000000000001</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
         <v>267</v>
       </c>
@@ -17086,23 +17080,23 @@
       <c r="C75" t="s">
         <v>417</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>45.083765999999997</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>-61.646531000000003</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>580</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>581</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
         <v>178</v>
       </c>
@@ -17112,23 +17106,23 @@
       <c r="C76" t="s">
         <v>417</v>
       </c>
-      <c r="D76">
+      <c r="E76">
         <v>45.101990000000001</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>-61.629950000000001</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>582</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>583</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
         <v>584</v>
       </c>
@@ -17138,26 +17132,26 @@
       <c r="C77" t="s">
         <v>412</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>45.731496</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>-60.209156</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>585</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>586</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>896</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="18" t="s">
         <v>199</v>
       </c>
@@ -17167,23 +17161,23 @@
       <c r="C78" t="s">
         <v>414</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>45.66</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>-62.411670000000001</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>587</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>588</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
         <v>105</v>
       </c>
@@ -17193,23 +17187,23 @@
       <c r="C79" t="s">
         <v>406</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>45.677680000000002</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>-61.912480000000002</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>589</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>590</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
         <v>106</v>
       </c>
@@ -17219,23 +17213,23 @@
       <c r="C80" t="s">
         <v>406</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>45.677619999999997</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>-61.912649999999999</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>591</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>592</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
         <v>107</v>
       </c>
@@ -17245,23 +17239,23 @@
       <c r="C81" t="s">
         <v>406</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>45.67756</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>-61.912820000000004</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>593</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>594</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="18" t="s">
         <v>124</v>
       </c>
@@ -17271,23 +17265,23 @@
       <c r="C82" t="s">
         <v>406</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>45.674799999999998</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>-61.907859999999999</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>595</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>596</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="18" t="s">
         <v>112</v>
       </c>
@@ -17297,23 +17291,23 @@
       <c r="C83" t="s">
         <v>419</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>44.010190000000001</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>-66.186179999999993</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>597</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>598</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
         <v>117</v>
       </c>
@@ -17323,23 +17317,23 @@
       <c r="C84" t="s">
         <v>420</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>43.686279999999996</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>-65.167810000000003</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>599</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>600</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
         <v>298</v>
       </c>
@@ -17349,23 +17343,23 @@
       <c r="C85" t="s">
         <v>411</v>
       </c>
-      <c r="D85">
+      <c r="E85">
         <v>44.623361000000003</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>-63.521050000000002</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>601</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>602</v>
       </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="18" t="s">
         <v>149</v>
       </c>
@@ -17375,23 +17369,23 @@
       <c r="C86" t="s">
         <v>406</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>45.690309999999997</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>-61.517310000000002</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>603</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>604</v>
       </c>
-      <c r="H86" t="s">
+      <c r="I86" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="18" t="s">
         <v>110</v>
       </c>
@@ -17401,23 +17395,23 @@
       <c r="C87" t="s">
         <v>417</v>
       </c>
-      <c r="D87">
+      <c r="E87">
         <v>45.084809999999997</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>-61.823639999999997</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>605</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>606</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="18" t="s">
         <v>209</v>
       </c>
@@ -17427,23 +17421,23 @@
       <c r="C88" t="s">
         <v>416</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>43.930929999999996</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>-66.16798</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>607</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>608</v>
       </c>
-      <c r="H88" t="s">
+      <c r="I88" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="18" t="s">
         <v>75</v>
       </c>
@@ -17453,23 +17447,23 @@
       <c r="C89" t="s">
         <v>411</v>
       </c>
-      <c r="D89">
+      <c r="E89">
         <v>44.634320000000002</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>-63.337209999999999</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>609</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>610</v>
       </c>
-      <c r="H89" t="s">
+      <c r="I89" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
         <v>125</v>
       </c>
@@ -17479,23 +17473,23 @@
       <c r="C90" t="s">
         <v>408</v>
       </c>
-      <c r="D90">
+      <c r="E90">
         <v>45.611289999999997</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>-60.984409999999997</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>611</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>612</v>
       </c>
-      <c r="H90" t="s">
+      <c r="I90" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="18" t="s">
         <v>143</v>
       </c>
@@ -17505,23 +17499,23 @@
       <c r="C91" t="s">
         <v>408</v>
       </c>
-      <c r="D91">
+      <c r="E91">
         <v>45.602600000000002</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>-60.902439999999999</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>613</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>614</v>
       </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
         <v>330</v>
       </c>
@@ -17531,17 +17525,17 @@
       <c r="C92" t="s">
         <v>413</v>
       </c>
-      <c r="D92">
+      <c r="E92">
         <v>45.904888999999997</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>-61.018250000000002</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="18" t="s">
         <v>78</v>
       </c>
@@ -17551,23 +17545,23 @@
       <c r="C93" t="s">
         <v>420</v>
       </c>
-      <c r="D93">
+      <c r="E93">
         <v>43.715719999999997</v>
       </c>
-      <c r="E93">
+      <c r="F93">
         <v>-65.008399999999995</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>615</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>616</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="18" t="s">
         <v>179</v>
       </c>
@@ -17577,26 +17571,26 @@
       <c r="C94" t="s">
         <v>414</v>
       </c>
-      <c r="D94">
+      <c r="E94">
         <v>45.650100000000002</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>-62.525089999999999</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>617</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>618</v>
       </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
         <v>894</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="18" t="s">
         <v>198</v>
       </c>
@@ -17606,23 +17600,23 @@
       <c r="C95" t="s">
         <v>408</v>
       </c>
-      <c r="D95">
+      <c r="E95">
         <v>45.560859999999998</v>
       </c>
-      <c r="E95">
+      <c r="F95">
         <v>-60.76126</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>620</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>621</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="18" t="s">
         <v>202</v>
       </c>
@@ -17632,23 +17626,23 @@
       <c r="C96" t="s">
         <v>414</v>
       </c>
-      <c r="D96">
+      <c r="E96">
         <v>45.660400000000003</v>
       </c>
-      <c r="E96">
+      <c r="F96">
         <v>-62.51482</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>622</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>623</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="18" t="s">
         <v>203</v>
       </c>
@@ -17658,23 +17652,23 @@
       <c r="C97" t="s">
         <v>414</v>
       </c>
-      <c r="D97">
+      <c r="E97">
         <v>45.660429999999998</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>-62.514870000000002</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>624</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>625</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="18" t="s">
         <v>204</v>
       </c>
@@ -17684,23 +17678,23 @@
       <c r="C98" t="s">
         <v>414</v>
       </c>
-      <c r="D98">
+      <c r="E98">
         <v>45.66046</v>
       </c>
-      <c r="E98">
+      <c r="F98">
         <v>-62.514919999999996</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>626</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>627</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="18" t="s">
         <v>628</v>
       </c>
@@ -17710,23 +17704,23 @@
       <c r="C99" t="s">
         <v>410</v>
       </c>
-      <c r="D99">
+      <c r="E99">
         <v>46.002760000000002</v>
       </c>
-      <c r="E99">
+      <c r="F99">
         <v>-60.96011</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>629</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>630</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="18" t="s">
         <v>180</v>
       </c>
@@ -17736,23 +17730,23 @@
       <c r="C100" t="s">
         <v>415</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>44.026119999999999</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>-64.665760000000006</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>631</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>632</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="18" t="s">
         <v>80</v>
       </c>
@@ -17762,23 +17756,23 @@
       <c r="C101" t="s">
         <v>416</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>43.679020000000001</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>-65.897800000000004</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>633</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>634</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="18" t="s">
         <v>185</v>
       </c>
@@ -17788,23 +17782,23 @@
       <c r="C102" t="s">
         <v>416</v>
       </c>
-      <c r="D102">
+      <c r="E102">
         <v>43.79083</v>
       </c>
-      <c r="E102">
+      <c r="F102">
         <v>-65.9114</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>635</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>636</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="18" t="s">
         <v>192</v>
       </c>
@@ -17814,23 +17808,23 @@
       <c r="C103" t="s">
         <v>416</v>
       </c>
-      <c r="D103">
+      <c r="E103">
         <v>43.72101</v>
       </c>
-      <c r="E103">
+      <c r="F103">
         <v>-65.845730000000003</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>637</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>638</v>
       </c>
-      <c r="H103" t="s">
+      <c r="I103" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="18" t="s">
         <v>639</v>
       </c>
@@ -17840,23 +17834,23 @@
       <c r="C104" t="s">
         <v>416</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>43.633560000000003</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>-66.030330000000006</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>640</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>641</v>
       </c>
-      <c r="H104" t="s">
+      <c r="I104" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="18" t="s">
         <v>197</v>
       </c>
@@ -17866,23 +17860,23 @@
       <c r="C105" t="s">
         <v>416</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>43.68282</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>-65.835809999999995</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>642</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>643</v>
       </c>
-      <c r="H105" t="s">
+      <c r="I105" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="18" t="s">
         <v>644</v>
       </c>
@@ -17892,23 +17886,23 @@
       <c r="C106" t="s">
         <v>416</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>43.637329999999999</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>-65.821860000000001</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>645</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>646</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="18" t="s">
         <v>230</v>
       </c>
@@ -17918,23 +17912,23 @@
       <c r="C107" t="s">
         <v>416</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>43.716079999999998</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>-65.942689999999999</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>647</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>648</v>
       </c>
-      <c r="H107" t="s">
+      <c r="I107" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="18" t="s">
         <v>233</v>
       </c>
@@ -17944,23 +17938,23 @@
       <c r="C108" t="s">
         <v>416</v>
       </c>
-      <c r="D108">
+      <c r="E108">
         <v>43.694020000000002</v>
       </c>
-      <c r="E108">
+      <c r="F108">
         <v>-65.959419999999994</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>649</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>650</v>
       </c>
-      <c r="H108" t="s">
+      <c r="I108" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="18" t="s">
         <v>320</v>
       </c>
@@ -17970,17 +17964,17 @@
       <c r="C109" t="s">
         <v>412</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>45.894472</v>
       </c>
-      <c r="E109">
+      <c r="F109">
         <v>-60.572277999999997</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="18">
         <v>1330</v>
       </c>
@@ -17990,23 +17984,23 @@
       <c r="C110" t="s">
         <v>413</v>
       </c>
-      <c r="D110">
+      <c r="E110">
         <v>46.08417</v>
       </c>
-      <c r="E110">
+      <c r="F110">
         <v>-61.45722</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>651</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>652</v>
       </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="18">
         <v>1331</v>
       </c>
@@ -18016,23 +18010,23 @@
       <c r="C111" t="s">
         <v>413</v>
       </c>
-      <c r="D111">
+      <c r="E111">
         <v>46.075470000000003</v>
       </c>
-      <c r="E111">
+      <c r="F111">
         <v>-61.447360000000003</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>653</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>654</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
         <v>327</v>
       </c>
@@ -18042,17 +18036,17 @@
       <c r="C112" t="s">
         <v>413</v>
       </c>
-      <c r="D112">
+      <c r="E112">
         <v>45.938861000000003</v>
       </c>
-      <c r="E112">
+      <c r="F112">
         <v>-61.107694000000002</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="18" t="s">
         <v>328</v>
       </c>
@@ -18062,17 +18056,17 @@
       <c r="C113" t="s">
         <v>410</v>
       </c>
-      <c r="D113">
+      <c r="E113">
         <v>46.048194000000002</v>
       </c>
-      <c r="E113">
+      <c r="F113">
         <v>-60.826582999999999</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="18" t="s">
         <v>325</v>
       </c>
@@ -18082,17 +18076,17 @@
       <c r="C114" t="s">
         <v>410</v>
       </c>
-      <c r="D114">
+      <c r="E114">
         <v>46.216917000000002</v>
       </c>
-      <c r="E114">
+      <c r="F114">
         <v>-60.597250000000003</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="18" t="s">
         <v>332</v>
       </c>
@@ -18102,17 +18096,17 @@
       <c r="C115" t="s">
         <v>413</v>
       </c>
-      <c r="D115">
+      <c r="E115">
         <v>45.874305999999997</v>
       </c>
-      <c r="E115">
+      <c r="F115">
         <v>-60.996583000000001</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="18" t="s">
         <v>334</v>
       </c>
@@ -18122,17 +18116,17 @@
       <c r="C116" t="s">
         <v>413</v>
       </c>
-      <c r="D116">
+      <c r="E116">
         <v>45.866</v>
       </c>
-      <c r="E116">
+      <c r="F116">
         <v>-61.059193999999998</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="18" t="s">
         <v>333</v>
       </c>
@@ -18142,17 +18136,17 @@
       <c r="C117" t="s">
         <v>413</v>
       </c>
-      <c r="D117">
+      <c r="E117">
         <v>45.870610999999997</v>
       </c>
-      <c r="E117">
+      <c r="F117">
         <v>-60.933971999999997</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="18" t="s">
         <v>142</v>
       </c>
@@ -18162,23 +18156,23 @@
       <c r="C118" t="s">
         <v>409</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>44.433439999999997</v>
       </c>
-      <c r="E118">
+      <c r="F118">
         <v>-64.131609999999995</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>655</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>656</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="18" t="s">
         <v>161</v>
       </c>
@@ -18188,23 +18182,23 @@
       <c r="C119" t="s">
         <v>409</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>44.437199999999997</v>
       </c>
-      <c r="E119">
+      <c r="F119">
         <v>-64.250579999999999</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>657</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>658</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="18" t="s">
         <v>211</v>
       </c>
@@ -18214,23 +18208,23 @@
       <c r="C120" t="s">
         <v>409</v>
       </c>
-      <c r="D120">
+      <c r="E120">
         <v>44.543570000000003</v>
       </c>
-      <c r="E120">
+      <c r="F120">
         <v>-64.173419999999993</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>659</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>660</v>
       </c>
-      <c r="H120" t="s">
+      <c r="I120" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="18" t="s">
         <v>231</v>
       </c>
@@ -18240,23 +18234,23 @@
       <c r="C121" t="s">
         <v>409</v>
       </c>
-      <c r="D121">
+      <c r="E121">
         <v>44.508870000000002</v>
       </c>
-      <c r="E121">
+      <c r="F121">
         <v>-64.13297</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>661</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
         <v>662</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="18">
         <v>28</v>
       </c>
@@ -18266,23 +18260,23 @@
       <c r="C122" t="s">
         <v>417</v>
       </c>
-      <c r="D122">
+      <c r="E122">
         <v>44.962499999999999</v>
       </c>
-      <c r="E122">
+      <c r="F122">
         <v>-62.060830000000003</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>663</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>664</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="18" t="s">
         <v>111</v>
       </c>
@@ -18292,23 +18286,23 @@
       <c r="C123" t="s">
         <v>417</v>
       </c>
-      <c r="D123">
+      <c r="E123">
         <v>44.950200000000002</v>
       </c>
-      <c r="E123">
+      <c r="F123">
         <v>-62.011069999999997</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>665</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>666</v>
       </c>
-      <c r="H123" t="s">
+      <c r="I123" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="18" t="s">
         <v>153</v>
       </c>
@@ -18318,23 +18312,23 @@
       <c r="C124" t="s">
         <v>417</v>
       </c>
-      <c r="D124">
+      <c r="E124">
         <v>44.962710000000001</v>
       </c>
-      <c r="E124">
+      <c r="F124">
         <v>-62.087910000000001</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>667</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>668</v>
       </c>
-      <c r="H124" t="s">
+      <c r="I124" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="18" t="s">
         <v>321</v>
       </c>
@@ -18344,17 +18338,17 @@
       <c r="C125" t="s">
         <v>410</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>45.930472000000002</v>
       </c>
-      <c r="E125">
+      <c r="F125">
         <v>-60.932222000000003</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="18" t="s">
         <v>174</v>
       </c>
@@ -18364,23 +18358,23 @@
       <c r="C126" t="s">
         <v>421</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>45.762810000000002</v>
       </c>
-      <c r="E126">
+      <c r="F126">
         <v>-63.351370000000003</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>669</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>670</v>
       </c>
-      <c r="H126" t="s">
+      <c r="I126" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="18" t="s">
         <v>175</v>
       </c>
@@ -18390,23 +18384,23 @@
       <c r="C127" t="s">
         <v>421</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>45.762819999999998</v>
       </c>
-      <c r="E127">
+      <c r="F127">
         <v>-63.351559999999999</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>671</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>672</v>
       </c>
-      <c r="H127" t="s">
+      <c r="I127" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="18" t="s">
         <v>176</v>
       </c>
@@ -18416,23 +18410,23 @@
       <c r="C128" t="s">
         <v>421</v>
       </c>
-      <c r="D128">
+      <c r="E128">
         <v>45.762839999999997</v>
       </c>
-      <c r="E128">
+      <c r="F128">
         <v>-63.351750000000003</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>673</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>674</v>
       </c>
-      <c r="H128" t="s">
+      <c r="I128" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="18" t="s">
         <v>33</v>
       </c>
@@ -18442,23 +18436,23 @@
       <c r="C129" t="s">
         <v>415</v>
       </c>
-      <c r="D129">
+      <c r="E129">
         <v>44.10013</v>
       </c>
-      <c r="E129">
+      <c r="F129">
         <v>-64.527829999999994</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>675</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>676</v>
       </c>
-      <c r="H129" t="s">
+      <c r="I129" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="18">
         <v>1369</v>
       </c>
@@ -18468,26 +18462,26 @@
       <c r="C130" t="s">
         <v>414</v>
       </c>
-      <c r="D130">
+      <c r="E130">
         <v>45.654697499999997</v>
       </c>
-      <c r="E130">
+      <c r="F130">
         <v>-62.429509400000001</v>
       </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>677</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>678</v>
       </c>
-      <c r="H130" t="s">
+      <c r="I130" t="s">
         <v>894</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="18" t="s">
         <v>108</v>
       </c>
@@ -18497,23 +18491,23 @@
       <c r="C131" t="s">
         <v>414</v>
       </c>
-      <c r="D131">
+      <c r="E131">
         <v>45.632129999999997</v>
       </c>
-      <c r="E131">
+      <c r="F131">
         <v>-62.505629999999996</v>
       </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
         <v>680</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>681</v>
       </c>
-      <c r="H131" t="s">
+      <c r="I131" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="18" t="s">
         <v>193</v>
       </c>
@@ -18523,23 +18517,23 @@
       <c r="C132" t="s">
         <v>414</v>
       </c>
-      <c r="D132">
+      <c r="E132">
         <v>45.643929999999997</v>
       </c>
-      <c r="E132">
+      <c r="F132">
         <v>-62.468119999999999</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>682</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>683</v>
       </c>
-      <c r="H132" t="s">
+      <c r="I132" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="18" t="s">
         <v>339</v>
       </c>
@@ -18549,23 +18543,23 @@
       <c r="C133" t="s">
         <v>408</v>
       </c>
-      <c r="D133">
+      <c r="E133">
         <v>45.566183000000002</v>
       </c>
-      <c r="E133">
+      <c r="F133">
         <v>-60.667299999999997</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>684</v>
       </c>
-      <c r="G133" t="s">
+      <c r="H133" t="s">
         <v>685</v>
       </c>
-      <c r="H133" t="s">
+      <c r="I133" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="18" t="s">
         <v>182</v>
       </c>
@@ -18575,26 +18569,26 @@
       <c r="C134" t="s">
         <v>406</v>
       </c>
-      <c r="D134">
+      <c r="E134">
         <v>45.654890000000002</v>
       </c>
-      <c r="E134">
+      <c r="F134">
         <v>-61.82873</v>
       </c>
-      <c r="F134" t="s">
+      <c r="G134" t="s">
         <v>686</v>
       </c>
-      <c r="G134" t="s">
+      <c r="H134" t="s">
         <v>687</v>
       </c>
-      <c r="H134" t="s">
+      <c r="I134" t="s">
         <v>894</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="18" t="s">
         <v>335</v>
       </c>
@@ -18604,17 +18598,17 @@
       <c r="C135" t="s">
         <v>413</v>
       </c>
-      <c r="D135">
+      <c r="E135">
         <v>45.908332999999999</v>
       </c>
-      <c r="E135">
+      <c r="F135">
         <v>-61.035806000000001</v>
       </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="18" t="s">
         <v>150</v>
       </c>
@@ -18624,23 +18618,23 @@
       <c r="C136" t="s">
         <v>420</v>
       </c>
-      <c r="D136">
+      <c r="E136">
         <v>43.524349999999998</v>
       </c>
-      <c r="E136">
+      <c r="F136">
         <v>-65.355500000000006</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
         <v>689</v>
       </c>
-      <c r="G136" t="s">
+      <c r="H136" t="s">
         <v>690</v>
       </c>
-      <c r="H136" t="s">
+      <c r="I136" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="18" t="s">
         <v>268</v>
       </c>
@@ -18650,23 +18644,23 @@
       <c r="C137" t="s">
         <v>417</v>
       </c>
-      <c r="D137">
+      <c r="E137">
         <v>45.159702000000003</v>
       </c>
-      <c r="E137">
+      <c r="F137">
         <v>-61.403179000000002</v>
       </c>
-      <c r="F137" t="s">
+      <c r="G137" t="s">
         <v>691</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>692</v>
       </c>
-      <c r="H137" t="s">
+      <c r="I137" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="18" t="s">
         <v>222</v>
       </c>
@@ -18676,23 +18670,23 @@
       <c r="C138" t="s">
         <v>417</v>
       </c>
-      <c r="D138">
+      <c r="E138">
         <v>45.155050000000003</v>
       </c>
-      <c r="E138">
+      <c r="F138">
         <v>-61.398519999999998</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>693</v>
       </c>
-      <c r="G138" t="s">
+      <c r="H138" t="s">
         <v>694</v>
       </c>
-      <c r="H138" t="s">
+      <c r="I138" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="18" t="s">
         <v>341</v>
       </c>
@@ -18702,23 +18696,23 @@
       <c r="C139" t="s">
         <v>410</v>
       </c>
-      <c r="D139">
+      <c r="E139">
         <v>46.664850000000001</v>
       </c>
-      <c r="E139">
+      <c r="F139">
         <v>-60.376649999999998</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>695</v>
       </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>696</v>
       </c>
-      <c r="H139" t="s">
+      <c r="I139" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="18" t="s">
         <v>344</v>
       </c>
@@ -18728,23 +18722,23 @@
       <c r="C140" t="s">
         <v>413</v>
       </c>
-      <c r="D140">
+      <c r="E140">
         <v>46.092483000000001</v>
       </c>
-      <c r="E140">
+      <c r="F140">
         <v>-61.505282999999999</v>
       </c>
-      <c r="F140" t="s">
+      <c r="G140" t="s">
         <v>697</v>
       </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>698</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I140" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="18">
         <v>745</v>
       </c>
@@ -18754,23 +18748,23 @@
       <c r="C141" t="s">
         <v>410</v>
       </c>
-      <c r="D141">
+      <c r="E141">
         <v>46.0854</v>
       </c>
-      <c r="E141">
+      <c r="F141">
         <v>-60.89284</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>699</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>700</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="18" t="s">
         <v>322</v>
       </c>
@@ -18780,17 +18774,17 @@
       <c r="C142" t="s">
         <v>410</v>
       </c>
-      <c r="D142">
+      <c r="E142">
         <v>46.080249999999999</v>
       </c>
-      <c r="E142">
+      <c r="F142">
         <v>-60.876832999999998</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="18" t="s">
         <v>523</v>
       </c>
@@ -18800,26 +18794,26 @@
       <c r="C143" t="s">
         <v>410</v>
       </c>
-      <c r="D143">
+      <c r="E143">
         <v>46.078710000000001</v>
       </c>
-      <c r="E143">
+      <c r="F143">
         <v>-60.888930000000002</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>524</v>
       </c>
-      <c r="G143" t="s">
+      <c r="H143" t="s">
         <v>525</v>
       </c>
-      <c r="H143" t="s">
+      <c r="I143" t="s">
         <v>895</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="18" t="s">
         <v>701</v>
       </c>
@@ -18829,23 +18823,23 @@
       <c r="C144" t="s">
         <v>413</v>
       </c>
-      <c r="D144">
+      <c r="E144">
         <v>46.676566999999999</v>
       </c>
-      <c r="E144">
+      <c r="F144">
         <v>-60.967883</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>702</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>703</v>
       </c>
-      <c r="H144" t="s">
+      <c r="I144" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="18" t="s">
         <v>704</v>
       </c>
@@ -18855,23 +18849,23 @@
       <c r="C145" t="s">
         <v>413</v>
       </c>
-      <c r="D145">
+      <c r="E145">
         <v>46.449800000000003</v>
       </c>
-      <c r="E145">
+      <c r="F145">
         <v>-61.117100000000001</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>705</v>
       </c>
-      <c r="G145" t="s">
+      <c r="H145" t="s">
         <v>706</v>
       </c>
-      <c r="H145" t="s">
+      <c r="I145" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="18" t="s">
         <v>194</v>
       </c>
@@ -18881,26 +18875,26 @@
       <c r="C146" t="s">
         <v>411</v>
       </c>
-      <c r="D146">
+      <c r="E146">
         <v>44.734119999999997</v>
       </c>
-      <c r="E146">
+      <c r="F146">
         <v>-62.810119999999998</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>707</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>708</v>
       </c>
-      <c r="H146" t="s">
+      <c r="I146" t="s">
         <v>894</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="18" t="s">
         <v>710</v>
       </c>
@@ -18910,23 +18904,23 @@
       <c r="C147" t="s">
         <v>411</v>
       </c>
-      <c r="D147">
+      <c r="E147">
         <v>44.463070000000002</v>
       </c>
-      <c r="E147">
+      <c r="F147">
         <v>-63.677399999999999</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>711</v>
       </c>
-      <c r="G147" t="s">
+      <c r="H147" t="s">
         <v>712</v>
       </c>
-      <c r="H147" t="s">
+      <c r="I147" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="18" t="s">
         <v>713</v>
       </c>
@@ -18936,23 +18930,23 @@
       <c r="C148" t="s">
         <v>406</v>
       </c>
-      <c r="D148">
+      <c r="E148">
         <v>45.611930000000001</v>
       </c>
-      <c r="E148">
+      <c r="F148">
         <v>-61.786769999999997</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>714</v>
       </c>
-      <c r="G148" t="s">
+      <c r="H148" t="s">
         <v>715</v>
       </c>
-      <c r="H148" t="s">
+      <c r="I148" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="18" t="s">
         <v>219</v>
       </c>
@@ -18962,26 +18956,26 @@
       <c r="C149" t="s">
         <v>420</v>
       </c>
-      <c r="D149">
+      <c r="E149">
         <v>43.468299999999999</v>
       </c>
-      <c r="E149">
+      <c r="F149">
         <v>-65.433040000000005</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>716</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>717</v>
       </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
         <v>894</v>
       </c>
-      <c r="I149" t="s">
+      <c r="J149" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="18" t="s">
         <v>220</v>
       </c>
@@ -18991,23 +18985,23 @@
       <c r="C150" t="s">
         <v>420</v>
       </c>
-      <c r="D150">
+      <c r="E150">
         <v>43.46743</v>
       </c>
-      <c r="E150">
+      <c r="F150">
         <v>-65.422830000000005</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>719</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" t="s">
         <v>720</v>
       </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="18" t="s">
         <v>721</v>
       </c>
@@ -19017,23 +19011,23 @@
       <c r="C151" t="s">
         <v>415</v>
       </c>
-      <c r="D151">
+      <c r="E151">
         <v>43.942858999999999</v>
       </c>
-      <c r="E151">
+      <c r="F151">
         <v>-64.723337000000001</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>722</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
         <v>723</v>
       </c>
-      <c r="H151" t="s">
+      <c r="I151" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="18" t="s">
         <v>724</v>
       </c>
@@ -19043,23 +19037,23 @@
       <c r="C152" t="s">
         <v>420</v>
       </c>
-      <c r="D152">
+      <c r="E152">
         <v>43.685746999999999</v>
       </c>
-      <c r="E152">
+      <c r="F152">
         <v>-65.018190000000004</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>725</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>726</v>
       </c>
-      <c r="H152" t="s">
+      <c r="I152" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="18" t="s">
         <v>331</v>
       </c>
@@ -19069,17 +19063,17 @@
       <c r="C153" t="s">
         <v>413</v>
       </c>
-      <c r="D153">
+      <c r="E153">
         <v>45.751083000000001</v>
       </c>
-      <c r="E153">
+      <c r="F153">
         <v>-61.153972000000003</v>
       </c>
-      <c r="I153" t="s">
+      <c r="J153" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="18" t="s">
         <v>115</v>
       </c>
@@ -19089,23 +19083,23 @@
       <c r="C154" t="s">
         <v>416</v>
       </c>
-      <c r="D154">
+      <c r="E154">
         <v>43.81344</v>
       </c>
-      <c r="E154">
+      <c r="F154">
         <v>-65.912139999999994</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>727</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>728</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="18" t="s">
         <v>157</v>
       </c>
@@ -19115,23 +19109,23 @@
       <c r="C155" t="s">
         <v>415</v>
       </c>
-      <c r="D155">
+      <c r="E155">
         <v>43.799370000000003</v>
       </c>
-      <c r="E155">
+      <c r="F155">
         <v>-64.879019999999997</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>729</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>730</v>
       </c>
-      <c r="H155" t="s">
+      <c r="I155" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="18" t="s">
         <v>93</v>
       </c>
@@ -19141,23 +19135,23 @@
       <c r="C156" t="s">
         <v>411</v>
       </c>
-      <c r="D156">
+      <c r="E156">
         <v>44.501170000000002</v>
       </c>
-      <c r="E156">
+      <c r="F156">
         <v>-63.814149999999998</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>731</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" t="s">
         <v>732</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="18" t="s">
         <v>733</v>
       </c>
@@ -19167,23 +19161,23 @@
       <c r="C157" t="s">
         <v>420</v>
       </c>
-      <c r="D157">
+      <c r="E157">
         <v>43.469050000000003</v>
       </c>
-      <c r="E157">
+      <c r="F157">
         <v>-65.740219999999994</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>734</v>
       </c>
-      <c r="G157" t="s">
+      <c r="H157" t="s">
         <v>735</v>
       </c>
-      <c r="H157" t="s">
+      <c r="I157" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="18" t="s">
         <v>137</v>
       </c>
@@ -19193,23 +19187,23 @@
       <c r="C158" t="s">
         <v>411</v>
       </c>
-      <c r="D158">
+      <c r="E158">
         <v>44.838590000000003</v>
       </c>
-      <c r="E158">
+      <c r="F158">
         <v>-62.511699999999998</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>736</v>
       </c>
-      <c r="G158" t="s">
+      <c r="H158" t="s">
         <v>737</v>
       </c>
-      <c r="H158" t="s">
+      <c r="I158" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="18" t="s">
         <v>177</v>
       </c>
@@ -19219,23 +19213,23 @@
       <c r="C159" t="s">
         <v>420</v>
       </c>
-      <c r="D159">
+      <c r="E159">
         <v>43.630749999999999</v>
       </c>
-      <c r="E159">
+      <c r="F159">
         <v>-65.260760000000005</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
         <v>738</v>
       </c>
-      <c r="G159" t="s">
+      <c r="H159" t="s">
         <v>739</v>
       </c>
-      <c r="H159" t="s">
+      <c r="I159" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="18" t="s">
         <v>740</v>
       </c>
@@ -19245,23 +19239,23 @@
       <c r="C160" t="s">
         <v>409</v>
       </c>
-      <c r="D160">
+      <c r="E160">
         <v>44.220357999999997</v>
       </c>
-      <c r="E160">
+      <c r="F160">
         <v>-64.308519000000004</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>741</v>
       </c>
-      <c r="G160" t="s">
+      <c r="H160" t="s">
         <v>742</v>
       </c>
-      <c r="H160" t="s">
+      <c r="I160" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="18" t="s">
         <v>118</v>
       </c>
@@ -19271,23 +19265,23 @@
       <c r="C161" t="s">
         <v>411</v>
       </c>
-      <c r="D161">
+      <c r="E161">
         <v>44.773110000000003</v>
       </c>
-      <c r="E161">
+      <c r="F161">
         <v>-62.725850000000001</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>743</v>
       </c>
-      <c r="G161" t="s">
+      <c r="H161" t="s">
         <v>744</v>
       </c>
-      <c r="H161" t="s">
+      <c r="I161" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="18" t="s">
         <v>276</v>
       </c>
@@ -19297,23 +19291,23 @@
       <c r="C162" t="s">
         <v>411</v>
       </c>
-      <c r="D162">
+      <c r="E162">
         <v>44.91053333</v>
       </c>
-      <c r="E162">
+      <c r="F162">
         <v>-62.319983329999999</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>745</v>
       </c>
-      <c r="G162" t="s">
+      <c r="H162" t="s">
         <v>746</v>
       </c>
-      <c r="H162" t="s">
+      <c r="I162" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="18">
         <v>1323</v>
       </c>
@@ -19323,23 +19317,23 @@
       <c r="C163" t="s">
         <v>411</v>
       </c>
-      <c r="D163">
+      <c r="E163">
         <v>44.845190000000002</v>
       </c>
-      <c r="E163">
+      <c r="F163">
         <v>-62.466290000000001</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>747</v>
       </c>
-      <c r="G163" t="s">
+      <c r="H163" t="s">
         <v>748</v>
       </c>
-      <c r="H163" t="s">
+      <c r="I163" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="18" t="s">
         <v>212</v>
       </c>
@@ -19349,23 +19343,23 @@
       <c r="C164" t="s">
         <v>411</v>
       </c>
-      <c r="D164">
+      <c r="E164">
         <v>44.838839999999998</v>
       </c>
-      <c r="E164">
+      <c r="F164">
         <v>-62.471069999999997</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>749</v>
       </c>
-      <c r="G164" t="s">
+      <c r="H164" t="s">
         <v>750</v>
       </c>
-      <c r="H164" t="s">
+      <c r="I164" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="18" t="s">
         <v>319</v>
       </c>
@@ -19375,17 +19369,17 @@
       <c r="C165" t="s">
         <v>408</v>
       </c>
-      <c r="D165">
+      <c r="E165">
         <v>45.696666999999998</v>
       </c>
-      <c r="E165">
+      <c r="F165">
         <v>-60.7425</v>
       </c>
-      <c r="I165" t="s">
+      <c r="J165" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="18" t="s">
         <v>214</v>
       </c>
@@ -19395,23 +19389,23 @@
       <c r="C166" t="s">
         <v>411</v>
       </c>
-      <c r="D166">
+      <c r="E166">
         <v>44.817929999999997</v>
       </c>
-      <c r="E166">
+      <c r="F166">
         <v>-62.618989999999997</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>751</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" t="s">
         <v>752</v>
       </c>
-      <c r="H166" t="s">
+      <c r="I166" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="18" t="s">
         <v>753</v>
       </c>
@@ -19421,23 +19415,23 @@
       <c r="C167" t="s">
         <v>410</v>
       </c>
-      <c r="D167">
+      <c r="E167">
         <v>46.263739999999999</v>
       </c>
-      <c r="E167">
+      <c r="F167">
         <v>-60.554929999999999</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>754</v>
       </c>
-      <c r="G167" t="s">
+      <c r="H167" t="s">
         <v>755</v>
       </c>
-      <c r="H167" t="s">
+      <c r="I167" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="18" t="s">
         <v>259</v>
       </c>
@@ -19447,23 +19441,23 @@
       <c r="C168" t="s">
         <v>406</v>
       </c>
-      <c r="D168">
+      <c r="E168">
         <v>45.708033</v>
       </c>
-      <c r="E168">
+      <c r="F168">
         <v>-61.856532999999999</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>756</v>
       </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
         <v>757</v>
       </c>
-      <c r="H168" t="s">
+      <c r="I168" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="18" t="s">
         <v>260</v>
       </c>
@@ -19473,23 +19467,23 @@
       <c r="C169" t="s">
         <v>406</v>
       </c>
-      <c r="D169">
+      <c r="E169">
         <v>45.694699999999997</v>
       </c>
-      <c r="E169">
+      <c r="F169">
         <v>-61.850067000000003</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>758</v>
       </c>
-      <c r="G169" t="s">
+      <c r="H169" t="s">
         <v>759</v>
       </c>
-      <c r="H169" t="s">
+      <c r="I169" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="18" t="s">
         <v>261</v>
       </c>
@@ -19499,23 +19493,23 @@
       <c r="C170" t="s">
         <v>406</v>
       </c>
-      <c r="D170">
+      <c r="E170">
         <v>45.698683000000003</v>
       </c>
-      <c r="E170">
+      <c r="F170">
         <v>-61.863999999999997</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>760</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>761</v>
       </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="18" t="s">
         <v>116</v>
       </c>
@@ -19525,23 +19519,23 @@
       <c r="C171" t="s">
         <v>409</v>
       </c>
-      <c r="D171">
+      <c r="E171">
         <v>44.570010000000003</v>
       </c>
-      <c r="E171">
+      <c r="F171">
         <v>-64.034459999999996</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>762</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>763</v>
       </c>
-      <c r="H171" t="s">
+      <c r="I171" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="18" t="s">
         <v>764</v>
       </c>
@@ -19551,23 +19545,23 @@
       <c r="C172" t="s">
         <v>409</v>
       </c>
-      <c r="D172">
+      <c r="E172">
         <v>44.514637999999998</v>
       </c>
-      <c r="E172">
+      <c r="F172">
         <v>-63.977783000000002</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>765</v>
       </c>
-      <c r="G172" t="s">
+      <c r="H172" t="s">
         <v>766</v>
       </c>
-      <c r="H172" t="s">
+      <c r="I172" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="18" t="s">
         <v>210</v>
       </c>
@@ -19577,23 +19571,23 @@
       <c r="C173" t="s">
         <v>411</v>
       </c>
-      <c r="D173">
+      <c r="E173">
         <v>44.557290000000002</v>
       </c>
-      <c r="E173">
+      <c r="F173">
         <v>-63.954230000000003</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>767</v>
       </c>
-      <c r="G173" t="s">
+      <c r="H173" t="s">
         <v>768</v>
       </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="18" t="s">
         <v>226</v>
       </c>
@@ -19603,23 +19597,23 @@
       <c r="C174" t="s">
         <v>409</v>
       </c>
-      <c r="D174">
+      <c r="E174">
         <v>44.548290000000001</v>
       </c>
-      <c r="E174">
+      <c r="F174">
         <v>-64.017420000000001</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>769</v>
       </c>
-      <c r="G174" t="s">
+      <c r="H174" t="s">
         <v>770</v>
       </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="18">
         <v>1012</v>
       </c>
@@ -19629,23 +19623,23 @@
       <c r="C175" t="s">
         <v>419</v>
       </c>
-      <c r="D175">
+      <c r="E175">
         <v>44.4071</v>
       </c>
-      <c r="E175">
+      <c r="F175">
         <v>-66.160529999999994</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>771</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>772</v>
       </c>
-      <c r="H175" t="s">
+      <c r="I175" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="18">
         <v>5007</v>
       </c>
@@ -19655,23 +19649,23 @@
       <c r="C176" t="s">
         <v>419</v>
       </c>
-      <c r="D176">
+      <c r="E176">
         <v>44.539119999999997</v>
       </c>
-      <c r="E176">
+      <c r="F176">
         <v>-65.957980000000006</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>773</v>
       </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
         <v>774</v>
       </c>
-      <c r="H176" t="s">
+      <c r="I176" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="18">
         <v>5008</v>
       </c>
@@ -19681,23 +19675,23 @@
       <c r="C177" t="s">
         <v>419</v>
       </c>
-      <c r="D177">
+      <c r="E177">
         <v>44.503839999999997</v>
       </c>
-      <c r="E177">
+      <c r="F177">
         <v>-65.932299999999998</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>775</v>
       </c>
-      <c r="G177" t="s">
+      <c r="H177" t="s">
         <v>776</v>
       </c>
-      <c r="H177" t="s">
+      <c r="I177" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="18" t="s">
         <v>127</v>
       </c>
@@ -19707,23 +19701,23 @@
       <c r="C178" t="s">
         <v>419</v>
       </c>
-      <c r="D178">
+      <c r="E178">
         <v>44.536239999999999</v>
       </c>
-      <c r="E178">
+      <c r="F178">
         <v>-66.001720000000006</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>777</v>
       </c>
-      <c r="G178" t="s">
+      <c r="H178" t="s">
         <v>778</v>
       </c>
-      <c r="H178" t="s">
+      <c r="I178" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="18" t="s">
         <v>128</v>
       </c>
@@ -19733,26 +19727,26 @@
       <c r="C179" t="s">
         <v>419</v>
       </c>
-      <c r="D179">
+      <c r="E179">
         <v>44.532800000000002</v>
       </c>
-      <c r="E179">
+      <c r="F179">
         <v>-65.984039999999993</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
         <v>779</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>780</v>
       </c>
-      <c r="H179" t="s">
+      <c r="I179" t="s">
         <v>894</v>
       </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="18" t="s">
         <v>129</v>
       </c>
@@ -19762,23 +19756,23 @@
       <c r="C180" t="s">
         <v>419</v>
       </c>
-      <c r="D180">
+      <c r="E180">
         <v>44.324019999999997</v>
       </c>
-      <c r="E180">
+      <c r="F180">
         <v>-66.135679999999994</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>782</v>
       </c>
-      <c r="G180" t="s">
+      <c r="H180" t="s">
         <v>783</v>
       </c>
-      <c r="H180" t="s">
+      <c r="I180" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="18" t="s">
         <v>130</v>
       </c>
@@ -19788,23 +19782,23 @@
       <c r="C181" t="s">
         <v>419</v>
       </c>
-      <c r="D181">
+      <c r="E181">
         <v>44.320149999999998</v>
       </c>
-      <c r="E181">
+      <c r="F181">
         <v>-66.135069999999999</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>784</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>785</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="18" t="s">
         <v>786</v>
       </c>
@@ -19814,23 +19808,23 @@
       <c r="C182" t="s">
         <v>419</v>
       </c>
-      <c r="D182">
+      <c r="E182">
         <v>44.38944</v>
       </c>
-      <c r="E182">
+      <c r="F182">
         <v>-66.176379999999995</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>787</v>
       </c>
-      <c r="G182" t="s">
+      <c r="H182" t="s">
         <v>788</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="18" t="s">
         <v>166</v>
       </c>
@@ -19840,23 +19834,23 @@
       <c r="C183" t="s">
         <v>419</v>
       </c>
-      <c r="D183">
+      <c r="E183">
         <v>44.401519999999998</v>
       </c>
-      <c r="E183">
+      <c r="F183">
         <v>-66.161270000000002</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>789</v>
       </c>
-      <c r="G183" t="s">
+      <c r="H183" t="s">
         <v>790</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="18" t="s">
         <v>167</v>
       </c>
@@ -19866,23 +19860,23 @@
       <c r="C184" t="s">
         <v>419</v>
       </c>
-      <c r="D184">
+      <c r="E184">
         <v>44.381839999999997</v>
       </c>
-      <c r="E184">
+      <c r="F184">
         <v>-66.177390000000003</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>791</v>
       </c>
-      <c r="G184" t="s">
+      <c r="H184" t="s">
         <v>792</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="18" t="s">
         <v>168</v>
       </c>
@@ -19892,26 +19886,26 @@
       <c r="C185" t="s">
         <v>419</v>
       </c>
-      <c r="D185">
+      <c r="E185">
         <v>44.350389999999997</v>
       </c>
-      <c r="E185">
+      <c r="F185">
         <v>-66.224670000000003</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>793</v>
       </c>
-      <c r="G185" t="s">
+      <c r="H185" t="s">
         <v>794</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>894</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="18" t="s">
         <v>169</v>
       </c>
@@ -19921,23 +19915,23 @@
       <c r="C186" t="s">
         <v>419</v>
       </c>
-      <c r="D186">
+      <c r="E186">
         <v>44.333500000000001</v>
       </c>
-      <c r="E186">
+      <c r="F186">
         <v>-66.201880000000003</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>796</v>
       </c>
-      <c r="G186" t="s">
+      <c r="H186" t="s">
         <v>797</v>
       </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="18" t="s">
         <v>798</v>
       </c>
@@ -19947,23 +19941,23 @@
       <c r="C187" t="s">
         <v>419</v>
       </c>
-      <c r="D187">
+      <c r="E187">
         <v>44.333199999999998</v>
       </c>
-      <c r="E187">
+      <c r="F187">
         <v>-66.243510000000001</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>799</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>800</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="18" t="s">
         <v>181</v>
       </c>
@@ -19973,23 +19967,23 @@
       <c r="C188" t="s">
         <v>419</v>
       </c>
-      <c r="D188">
+      <c r="E188">
         <v>44.386839999999999</v>
       </c>
-      <c r="E188">
+      <c r="F188">
         <v>-66.144239999999996</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>801</v>
       </c>
-      <c r="G188" t="s">
+      <c r="H188" t="s">
         <v>802</v>
       </c>
-      <c r="H188" t="s">
+      <c r="I188" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="18" t="s">
         <v>206</v>
       </c>
@@ -19999,26 +19993,26 @@
       <c r="C189" t="s">
         <v>419</v>
       </c>
-      <c r="D189">
+      <c r="E189">
         <v>44.485700000000001</v>
       </c>
-      <c r="E189">
+      <c r="F189">
         <v>-66.059460000000001</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>803</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>804</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>895</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="18" t="s">
         <v>163</v>
       </c>
@@ -20028,23 +20022,23 @@
       <c r="C190" t="s">
         <v>417</v>
       </c>
-      <c r="D190">
+      <c r="E190">
         <v>45.078110000000002</v>
       </c>
-      <c r="E190">
+      <c r="F190">
         <v>-61.93844</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>806</v>
       </c>
-      <c r="G190" t="s">
+      <c r="H190" t="s">
         <v>807</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="18" t="s">
         <v>164</v>
       </c>
@@ -20054,23 +20048,23 @@
       <c r="C191" t="s">
         <v>417</v>
       </c>
-      <c r="D191">
+      <c r="E191">
         <v>45.071190000000001</v>
       </c>
-      <c r="E191">
+      <c r="F191">
         <v>-61.926720000000003</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>808</v>
       </c>
-      <c r="G191" t="s">
+      <c r="H191" t="s">
         <v>809</v>
       </c>
-      <c r="H191" t="s">
+      <c r="I191" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="18" t="s">
         <v>165</v>
       </c>
@@ -20080,23 +20074,23 @@
       <c r="C192" t="s">
         <v>417</v>
       </c>
-      <c r="D192">
+      <c r="E192">
         <v>45.067889999999998</v>
       </c>
-      <c r="E192">
+      <c r="F192">
         <v>-61.914059999999999</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>810</v>
       </c>
-      <c r="G192" t="s">
+      <c r="H192" t="s">
         <v>811</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="18" t="s">
         <v>170</v>
       </c>
@@ -20106,26 +20100,26 @@
       <c r="C193" t="s">
         <v>417</v>
       </c>
-      <c r="D193">
+      <c r="E193">
         <v>45.071190000000001</v>
       </c>
-      <c r="E193">
+      <c r="F193">
         <v>-61.926720000000003</v>
       </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
         <v>808</v>
       </c>
-      <c r="G193" t="s">
+      <c r="H193" t="s">
         <v>809</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
         <v>894</v>
       </c>
-      <c r="I193" t="s">
+      <c r="J193" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="18">
         <v>778</v>
       </c>
@@ -20135,23 +20129,23 @@
       <c r="C194" t="s">
         <v>408</v>
       </c>
-      <c r="D194">
+      <c r="E194">
         <v>45.661830000000002</v>
       </c>
-      <c r="E194">
+      <c r="F194">
         <v>-60.847610000000003</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>813</v>
       </c>
-      <c r="G194" t="s">
+      <c r="H194" t="s">
         <v>814</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="18">
         <v>994</v>
       </c>
@@ -20161,23 +20155,23 @@
       <c r="C195" t="s">
         <v>408</v>
       </c>
-      <c r="D195">
+      <c r="E195">
         <v>45.655329999999999</v>
       </c>
-      <c r="E195">
+      <c r="F195">
         <v>-60.84581</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>815</v>
       </c>
-      <c r="G195" t="s">
+      <c r="H195" t="s">
         <v>816</v>
       </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="18" t="s">
         <v>121</v>
       </c>
@@ -20187,23 +20181,23 @@
       <c r="C196" t="s">
         <v>413</v>
       </c>
-      <c r="D196">
+      <c r="E196">
         <v>45.646880000000003</v>
       </c>
-      <c r="E196">
+      <c r="F196">
         <v>-61.411470000000001</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>817</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>818</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="18" t="s">
         <v>139</v>
       </c>
@@ -20213,23 +20207,23 @@
       <c r="C197" t="s">
         <v>417</v>
       </c>
-      <c r="D197">
+      <c r="E197">
         <v>45.525170000000003</v>
       </c>
-      <c r="E197">
+      <c r="F197">
         <v>-61.25535</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>819</v>
       </c>
-      <c r="G197" t="s">
+      <c r="H197" t="s">
         <v>820</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="18" t="s">
         <v>195</v>
       </c>
@@ -20239,23 +20233,23 @@
       <c r="C198" t="s">
         <v>417</v>
       </c>
-      <c r="D198">
+      <c r="E198">
         <v>45.589300000000001</v>
       </c>
-      <c r="E198">
+      <c r="F198">
         <v>-61.379440000000002</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>821</v>
       </c>
-      <c r="G198" t="s">
+      <c r="H198" t="s">
         <v>822</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="18" t="s">
         <v>196</v>
       </c>
@@ -20265,23 +20259,23 @@
       <c r="C199" t="s">
         <v>413</v>
       </c>
-      <c r="D199">
+      <c r="E199">
         <v>45.595860000000002</v>
       </c>
-      <c r="E199">
+      <c r="F199">
         <v>-61.363819999999997</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>823</v>
       </c>
-      <c r="G199" t="s">
+      <c r="H199" t="s">
         <v>824</v>
       </c>
-      <c r="H199" t="s">
+      <c r="I199" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="18" t="s">
         <v>825</v>
       </c>
@@ -20291,23 +20285,23 @@
       <c r="C200" t="s">
         <v>413</v>
       </c>
-      <c r="D200">
+      <c r="E200">
         <v>45.594499999999996</v>
       </c>
-      <c r="E200">
+      <c r="F200">
         <v>-61.363819999999997</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>826</v>
       </c>
-      <c r="G200" t="s">
+      <c r="H200" t="s">
         <v>824</v>
       </c>
-      <c r="H200" t="s">
+      <c r="I200" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="18" t="s">
         <v>891</v>
       </c>
@@ -20317,17 +20311,17 @@
       <c r="C201" t="s">
         <v>413</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>892</v>
       </c>
-      <c r="G201" t="s">
+      <c r="H201" t="s">
         <v>893</v>
       </c>
-      <c r="H201" t="s">
+      <c r="I201" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="18" t="s">
         <v>173</v>
       </c>
@@ -20337,23 +20331,23 @@
       <c r="C202" t="s">
         <v>421</v>
       </c>
-      <c r="D202">
+      <c r="E202">
         <v>45.783160000000002</v>
       </c>
-      <c r="E202">
+      <c r="F202">
         <v>-63.225169999999999</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>827</v>
       </c>
-      <c r="G202" t="s">
+      <c r="H202" t="s">
         <v>828</v>
       </c>
-      <c r="H202" t="s">
+      <c r="I202" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="18" t="s">
         <v>126</v>
       </c>
@@ -20363,26 +20357,26 @@
       <c r="C203" t="s">
         <v>417</v>
       </c>
-      <c r="D203">
+      <c r="E203">
         <v>45.225650000000002</v>
       </c>
-      <c r="E203">
+      <c r="F203">
         <v>-61.29616</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
         <v>829</v>
       </c>
-      <c r="G203" t="s">
+      <c r="H203" t="s">
         <v>830</v>
       </c>
-      <c r="H203" t="s">
+      <c r="I203" t="s">
         <v>895</v>
       </c>
-      <c r="I203" t="s">
+      <c r="J203" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="18" t="s">
         <v>140</v>
       </c>
@@ -20392,23 +20386,23 @@
       <c r="C204" t="s">
         <v>417</v>
       </c>
-      <c r="D204">
+      <c r="E204">
         <v>45.250070000000001</v>
       </c>
-      <c r="E204">
+      <c r="F204">
         <v>-61.298659999999998</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>832</v>
       </c>
-      <c r="G204" t="s">
+      <c r="H204" t="s">
         <v>833</v>
       </c>
-      <c r="H204" t="s">
+      <c r="I204" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="18" t="s">
         <v>155</v>
       </c>
@@ -20418,23 +20412,23 @@
       <c r="C205" t="s">
         <v>417</v>
       </c>
-      <c r="D205">
+      <c r="E205">
         <v>45.207680000000003</v>
       </c>
-      <c r="E205">
+      <c r="F205">
         <v>-61.353189999999998</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>834</v>
       </c>
-      <c r="G205" t="s">
+      <c r="H205" t="s">
         <v>835</v>
       </c>
-      <c r="H205" t="s">
+      <c r="I205" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="18" t="s">
         <v>218</v>
       </c>
@@ -20444,23 +20438,23 @@
       <c r="C206" t="s">
         <v>417</v>
       </c>
-      <c r="D206">
+      <c r="E206">
         <v>45.230179999999997</v>
       </c>
-      <c r="E206">
+      <c r="F206">
         <v>-61.253390000000003</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>836</v>
       </c>
-      <c r="G206" t="s">
+      <c r="H206" t="s">
         <v>837</v>
       </c>
-      <c r="H206" t="s">
+      <c r="I206" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="18" t="s">
         <v>227</v>
       </c>
@@ -20470,23 +20464,23 @@
       <c r="C207" t="s">
         <v>406</v>
       </c>
-      <c r="D207">
+      <c r="E207">
         <v>45.643909999999998</v>
       </c>
-      <c r="E207">
+      <c r="F207">
         <v>-61.647590000000001</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>838</v>
       </c>
-      <c r="G207" t="s">
+      <c r="H207" t="s">
         <v>839</v>
       </c>
-      <c r="H207" t="s">
+      <c r="I207" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="18" t="s">
         <v>228</v>
       </c>
@@ -20496,23 +20490,23 @@
       <c r="C208" t="s">
         <v>406</v>
       </c>
-      <c r="D208">
+      <c r="E208">
         <v>45.644039999999997</v>
       </c>
-      <c r="E208">
+      <c r="F208">
         <v>-61.647759999999998</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
         <v>840</v>
       </c>
-      <c r="G208" t="s">
+      <c r="H208" t="s">
         <v>841</v>
       </c>
-      <c r="H208" t="s">
+      <c r="I208" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="18" t="s">
         <v>229</v>
       </c>
@@ -20522,23 +20516,23 @@
       <c r="C209" t="s">
         <v>406</v>
       </c>
-      <c r="D209">
+      <c r="E209">
         <v>45.644170000000003</v>
       </c>
-      <c r="E209">
+      <c r="F209">
         <v>-61.647889999999997</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>842</v>
       </c>
-      <c r="G209" t="s">
+      <c r="H209" t="s">
         <v>843</v>
       </c>
-      <c r="H209" t="s">
+      <c r="I209" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="18">
         <v>1199</v>
       </c>
@@ -20548,26 +20542,26 @@
       <c r="C210" t="s">
         <v>417</v>
       </c>
-      <c r="D210">
+      <c r="E210">
         <v>45.274290000000001</v>
       </c>
-      <c r="E210">
+      <c r="F210">
         <v>-61.128439999999998</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>844</v>
       </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
         <v>845</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>894</v>
       </c>
-      <c r="I210" t="s">
+      <c r="J210" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="18" t="s">
         <v>109</v>
       </c>
@@ -20577,23 +20571,23 @@
       <c r="C211" t="s">
         <v>417</v>
       </c>
-      <c r="D211">
+      <c r="E211">
         <v>45.198680000000003</v>
       </c>
-      <c r="E211">
+      <c r="F211">
         <v>-61.188630000000003</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>847</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>848</v>
       </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="18" t="s">
         <v>119</v>
       </c>
@@ -20603,23 +20597,23 @@
       <c r="C212" t="s">
         <v>417</v>
       </c>
-      <c r="D212">
+      <c r="E212">
         <v>45.255710000000001</v>
       </c>
-      <c r="E212">
+      <c r="F212">
         <v>-61.146680000000003</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>849</v>
       </c>
-      <c r="G212" t="s">
+      <c r="H212" t="s">
         <v>850</v>
       </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="18" t="s">
         <v>141</v>
       </c>
@@ -20629,23 +20623,23 @@
       <c r="C213" t="s">
         <v>417</v>
       </c>
-      <c r="D213">
+      <c r="E213">
         <v>45.23997</v>
       </c>
-      <c r="E213">
+      <c r="F213">
         <v>-61.168379999999999</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>851</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>852</v>
       </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="18" t="s">
         <v>148</v>
       </c>
@@ -20655,23 +20649,23 @@
       <c r="C214" t="s">
         <v>417</v>
       </c>
-      <c r="D214">
+      <c r="E214">
         <v>45.23836</v>
       </c>
-      <c r="E214">
+      <c r="F214">
         <v>-61.150509999999997</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>853</v>
       </c>
-      <c r="G214" t="s">
+      <c r="H214" t="s">
         <v>854</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="18" t="s">
         <v>186</v>
       </c>
@@ -20681,23 +20675,23 @@
       <c r="C215" t="s">
         <v>417</v>
       </c>
-      <c r="D215">
+      <c r="E215">
         <v>45.239899999999999</v>
       </c>
-      <c r="E215">
+      <c r="F215">
         <v>-61.152700000000003</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>855</v>
       </c>
-      <c r="G215" t="s">
+      <c r="H215" t="s">
         <v>856</v>
       </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="18" t="s">
         <v>188</v>
       </c>
@@ -20707,23 +20701,23 @@
       <c r="C216" t="s">
         <v>417</v>
       </c>
-      <c r="D216">
+      <c r="E216">
         <v>45.270620000000001</v>
       </c>
-      <c r="E216">
+      <c r="F216">
         <v>-61.134999999999998</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>857</v>
       </c>
-      <c r="G216" t="s">
+      <c r="H216" t="s">
         <v>858</v>
       </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="18" t="s">
         <v>189</v>
       </c>
@@ -20733,23 +20727,23 @@
       <c r="C217" t="s">
         <v>417</v>
       </c>
-      <c r="D217">
+      <c r="E217">
         <v>45.286740000000002</v>
       </c>
-      <c r="E217">
+      <c r="F217">
         <v>-61.168349999999997</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>859</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>860</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="18" t="s">
         <v>221</v>
       </c>
@@ -20759,23 +20753,23 @@
       <c r="C218" t="s">
         <v>417</v>
       </c>
-      <c r="D218">
+      <c r="E218">
         <v>45.237589999999997</v>
       </c>
-      <c r="E218">
+      <c r="F218">
         <v>-61.149470000000001</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>861</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>862</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="18" t="s">
         <v>297</v>
       </c>
@@ -20785,23 +20779,23 @@
       <c r="C219" t="s">
         <v>417</v>
       </c>
-      <c r="D219">
+      <c r="E219">
         <v>45.239060000000002</v>
       </c>
-      <c r="E219">
+      <c r="F219">
         <v>-61.149619999999999</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>863</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>864</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="18" t="s">
         <v>223</v>
       </c>
@@ -20811,23 +20805,23 @@
       <c r="C220" t="s">
         <v>417</v>
       </c>
-      <c r="D220">
+      <c r="E220">
         <v>45.249290000000002</v>
       </c>
-      <c r="E220">
+      <c r="F220">
         <v>-61.146769999999997</v>
       </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>865</v>
       </c>
-      <c r="G220" t="s">
+      <c r="H220" t="s">
         <v>866</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="18" t="s">
         <v>235</v>
       </c>
@@ -20837,23 +20831,23 @@
       <c r="C221" t="s">
         <v>417</v>
       </c>
-      <c r="D221">
+      <c r="E221">
         <v>45.246490000000001</v>
       </c>
-      <c r="E221">
+      <c r="F221">
         <v>-61.156199999999998</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>867</v>
       </c>
-      <c r="G221" t="s">
+      <c r="H221" t="s">
         <v>868</v>
       </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="18" t="s">
         <v>236</v>
       </c>
@@ -20863,23 +20857,23 @@
       <c r="C222" t="s">
         <v>417</v>
       </c>
-      <c r="D222">
+      <c r="E222">
         <v>45.233609999999999</v>
       </c>
-      <c r="E222">
+      <c r="F222">
         <v>-61.158479999999997</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>869</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>870</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="18" t="s">
         <v>871</v>
       </c>
@@ -20889,23 +20883,23 @@
       <c r="C223" t="s">
         <v>413</v>
       </c>
-      <c r="D223">
+      <c r="E223">
         <v>45.951259999999998</v>
       </c>
-      <c r="E223">
+      <c r="F223">
         <v>-61.120710000000003</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>872</v>
       </c>
-      <c r="G223" t="s">
+      <c r="H223" t="s">
         <v>873</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="18" t="s">
         <v>874</v>
       </c>
@@ -20915,23 +20909,23 @@
       <c r="C224" t="s">
         <v>413</v>
       </c>
-      <c r="D224">
+      <c r="E224">
         <v>45.94547</v>
       </c>
-      <c r="E224">
+      <c r="F224">
         <v>-61.129170000000002</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>875</v>
       </c>
-      <c r="G224" t="s">
+      <c r="H224" t="s">
         <v>876</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="18" t="s">
         <v>132</v>
       </c>
@@ -20941,23 +20935,23 @@
       <c r="C225" t="s">
         <v>413</v>
       </c>
-      <c r="D225">
+      <c r="E225">
         <v>45.948509999999999</v>
       </c>
-      <c r="E225">
+      <c r="F225">
         <v>-61.124659999999999</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>877</v>
       </c>
-      <c r="G225" t="s">
+      <c r="H225" t="s">
         <v>878</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="18" t="s">
         <v>104</v>
       </c>
@@ -20967,23 +20961,23 @@
       <c r="C226" t="s">
         <v>413</v>
       </c>
-      <c r="D226">
+      <c r="E226">
         <v>45.976080000000003</v>
       </c>
-      <c r="E226">
+      <c r="F226">
         <v>-61.022680000000001</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>879</v>
       </c>
-      <c r="G226" t="s">
+      <c r="H226" t="s">
         <v>880</v>
       </c>
-      <c r="H226" t="s">
+      <c r="I226" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="18" t="s">
         <v>326</v>
       </c>
@@ -20993,17 +20987,17 @@
       <c r="C227" t="s">
         <v>413</v>
       </c>
-      <c r="D227">
+      <c r="E227">
         <v>45.979666999999999</v>
       </c>
-      <c r="E227">
+      <c r="F227">
         <v>-61.028832999999999</v>
       </c>
-      <c r="I227" t="s">
+      <c r="J227" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="18" t="s">
         <v>336</v>
       </c>
@@ -21013,17 +21007,17 @@
       <c r="C228" t="s">
         <v>413</v>
       </c>
-      <c r="D228">
+      <c r="E228">
         <v>45.957861000000001</v>
       </c>
-      <c r="E228">
+      <c r="F228">
         <v>-61.001582999999997</v>
       </c>
-      <c r="I228" t="s">
+      <c r="J228" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="18" t="s">
         <v>101</v>
       </c>
@@ -21033,23 +21027,23 @@
       <c r="C229" t="s">
         <v>417</v>
       </c>
-      <c r="D229">
+      <c r="E229">
         <v>45.072290000000002</v>
       </c>
-      <c r="E229">
+      <c r="F229">
         <v>-61.86092</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>881</v>
       </c>
-      <c r="G229" t="s">
+      <c r="H229" t="s">
         <v>882</v>
       </c>
-      <c r="H229" t="s">
+      <c r="I229" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="18" t="s">
         <v>120</v>
       </c>
@@ -21059,23 +21053,23 @@
       <c r="C230" t="s">
         <v>420</v>
       </c>
-      <c r="D230">
+      <c r="E230">
         <v>43.497140000000002</v>
       </c>
-      <c r="E230">
+      <c r="F230">
         <v>-65.737840000000006</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>883</v>
       </c>
-      <c r="G230" t="s">
+      <c r="H230" t="s">
         <v>884</v>
       </c>
-      <c r="H230" t="s">
+      <c r="I230" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="18" t="s">
         <v>919</v>
       </c>
@@ -21085,19 +21079,19 @@
       <c r="C231" t="s">
         <v>419</v>
       </c>
-      <c r="F231" t="s">
+      <c r="G231" t="s">
         <v>920</v>
       </c>
-      <c r="G231" t="s">
+      <c r="H231" t="s">
         <v>921</v>
       </c>
-      <c r="H231" t="s">
+      <c r="I231" t="s">
         <v>895</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I225" xr:uid="{F9178D97-480E-4A1C-A868-3FF779D47BC0}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I230">
+  <autoFilter ref="A1:J225" xr:uid="{F9178D97-480E-4A1C-A868-3FF779D47BC0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J230">
       <sortCondition ref="B1:B225"/>
     </sortState>
   </autoFilter>
@@ -21109,16 +21103,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093BE4C6-3F93-489F-ACED-C7B3A538ED98}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="140.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="134.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="140.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="134.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>347</v>
       </c>
@@ -21135,7 +21129,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>254</v>
       </c>
@@ -21150,7 +21144,7 @@
       </c>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
@@ -21167,7 +21161,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>405</v>
       </c>
@@ -21178,7 +21172,7 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>0</v>
       </c>
@@ -21195,7 +21189,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
@@ -21208,7 +21202,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>3</v>
       </c>
@@ -21223,7 +21217,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>4</v>
       </c>
@@ -21238,7 +21232,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>5</v>
       </c>
@@ -21253,7 +21247,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
@@ -21268,7 +21262,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>7</v>
       </c>
@@ -21283,7 +21277,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>8</v>
       </c>
@@ -21298,7 +21292,7 @@
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>9</v>
       </c>
@@ -21313,7 +21307,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>10</v>
       </c>
@@ -21328,7 +21322,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>11</v>
       </c>
@@ -21343,7 +21337,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>251</v>
       </c>
@@ -21358,7 +21352,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>250</v>
       </c>
@@ -21373,7 +21367,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>252</v>
       </c>
@@ -21388,7 +21382,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>253</v>
       </c>
@@ -21403,7 +21397,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>12</v>
       </c>
@@ -21418,7 +21412,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -21431,7 +21425,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>14</v>
       </c>
@@ -21444,7 +21438,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>16</v>
       </c>
@@ -21459,7 +21453,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>17</v>
       </c>
@@ -21472,7 +21466,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>15</v>
       </c>
@@ -21487,7 +21481,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>18</v>
       </c>
@@ -21502,7 +21496,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>20</v>
       </c>
@@ -21515,7 +21509,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
         <v>19</v>
       </c>
@@ -21530,7 +21524,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>23</v>
       </c>
@@ -21545,7 +21539,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>24</v>
       </c>
@@ -21560,7 +21554,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -21575,7 +21569,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>886</v>
       </c>
@@ -21590,7 +21584,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>885</v>
       </c>
@@ -21603,7 +21597,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>21</v>
       </c>
@@ -21616,7 +21610,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
         <v>22</v>
       </c>
@@ -21629,7 +21623,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -21644,7 +21638,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -21657,7 +21651,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>30</v>
       </c>
@@ -21672,7 +21666,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
         <v>27</v>
       </c>
@@ -21685,7 +21679,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
         <v>28</v>
       </c>
@@ -21698,7 +21692,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
         <v>31</v>
       </c>
